--- a/artfynd/S 1278-2025 artfynd.xlsx
+++ b/artfynd/S 1278-2025 artfynd.xlsx
@@ -3380,7 +3380,7 @@
         <v>136125996</v>
       </c>
       <c r="B26" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1278-2025 artfynd.xlsx
+++ b/artfynd/S 1278-2025 artfynd.xlsx
@@ -3380,7 +3380,7 @@
         <v>136125996</v>
       </c>
       <c r="B26" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1278-2025 artfynd.xlsx
+++ b/artfynd/S 1278-2025 artfynd.xlsx
@@ -3380,7 +3380,7 @@
         <v>136125996</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
